--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tuenl-my.sharepoint.com/personal/f_nardella_student_tue_nl/Documents/INNO Energy/UPC Energy Policy/TIMES_ses/MSc_SELECT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\MSc_SELECT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{13D91245-91CE-4E87-951E-9ABEA10B1F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD770827-29AB-40B2-BFE0-E7FECA6538BE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A0A0EF-9960-4507-96F1-622A24A8D56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="853" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" tabRatio="853" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Region-Time Slices" sheetId="16" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="403">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -1266,6 +1266,15 @@
   </si>
   <si>
     <t>4W7SU8</t>
+  </si>
+  <si>
+    <t>ELC~1</t>
+  </si>
+  <si>
+    <t>COMPRD~1</t>
+  </si>
+  <si>
+    <t>ELC~3</t>
   </si>
 </sst>
 </file>
@@ -3947,6 +3956,7 @@
     <cellStyle name="Neutralne 8" xfId="452" xr:uid="{00000000-0005-0000-0000-0000C3010000}"/>
     <cellStyle name="Neutralne 9" xfId="453" xr:uid="{00000000-0005-0000-0000-0000C4010000}"/>
     <cellStyle name="no dec" xfId="454" xr:uid="{00000000-0005-0000-0000-0000C5010000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal - Style1" xfId="455" xr:uid="{00000000-0005-0000-0000-0000C6010000}"/>
     <cellStyle name="Normal 10" xfId="456" xr:uid="{00000000-0005-0000-0000-0000C7010000}"/>
     <cellStyle name="Normal 10 2" xfId="723" xr:uid="{EB0C2ED4-4687-4FED-8497-A80B55395A75}"/>
@@ -3970,7 +3980,6 @@
     <cellStyle name="Normal GHG-Shade" xfId="473" xr:uid="{00000000-0005-0000-0000-0000D8010000}"/>
     <cellStyle name="Normal GHG-Shade 2" xfId="474" xr:uid="{00000000-0005-0000-0000-0000D9010000}"/>
     <cellStyle name="Normal_Constants 2" xfId="722" xr:uid="{C6AA90A5-1043-4AB8-B229-DB93742915B6}"/>
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
     <cellStyle name="Normalny 10" xfId="475" xr:uid="{00000000-0005-0000-0000-0000DD010000}"/>
     <cellStyle name="Normalny 10 2" xfId="476" xr:uid="{00000000-0005-0000-0000-0000DE010000}"/>
     <cellStyle name="Normalny 11" xfId="477" xr:uid="{00000000-0005-0000-0000-0000DF010000}"/>
@@ -4656,13 +4665,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:G63"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" customWidth="1"/>
-    <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.109375" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.86328125" customWidth="1"/>
+    <col min="2" max="2" width="19.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.1328125" customWidth="1"/>
+    <col min="5" max="5" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.53125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4672,7 +4681,7 @@
     <row r="3" spans="2:7" ht="12.75" customHeight="1">
       <c r="B3" s="4"/>
     </row>
-    <row r="4" spans="2:7" ht="17.399999999999999">
+    <row r="4" spans="2:7" ht="17.25">
       <c r="B4" s="5" t="s">
         <v>138</v>
       </c>
@@ -4681,7 +4690,7 @@
       </c>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" ht="13.15">
       <c r="B5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="2"/>
@@ -5134,14 +5143,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:I44"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" customWidth="1"/>
+    <col min="1" max="1" width="2.86328125" customWidth="1"/>
+    <col min="2" max="2" width="20.1328125" customWidth="1"/>
     <col min="3" max="3" width="14.33203125" customWidth="1"/>
     <col min="4" max="4" width="9.6640625" customWidth="1"/>
     <col min="5" max="5" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15">
@@ -5260,7 +5269,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="13.8" thickBot="1">
+    <row r="27" spans="2:9" ht="13.15" thickBot="1">
       <c r="B27" s="13"/>
       <c r="I27">
         <v>2033</v>
@@ -5365,15 +5374,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:I32"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" customWidth="1"/>
+    <col min="1" max="1" width="2.86328125" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="17.399999999999999">
+    <row r="2" spans="2:9" ht="17.25">
       <c r="B2" s="5" t="s">
         <v>149</v>
       </c>
@@ -5486,7 +5495,7 @@
       <c r="I9" s="11"/>
     </row>
     <row r="10" spans="2:9" ht="12.75" customHeight="1"/>
-    <row r="11" spans="2:9" ht="17.399999999999999">
+    <row r="11" spans="2:9" ht="17.25">
       <c r="B11" s="5" t="s">
         <v>151</v>
       </c>
@@ -5718,13 +5727,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:O37"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" customWidth="1"/>
+    <col min="1" max="1" width="2.86328125" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" customWidth="1"/>
-    <col min="4" max="4" width="31.44140625" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" customWidth="1"/>
+    <col min="3" max="3" width="14.46484375" customWidth="1"/>
+    <col min="4" max="4" width="31.46484375" customWidth="1"/>
+    <col min="5" max="5" width="11.53125" customWidth="1"/>
     <col min="7" max="7" width="59.33203125" customWidth="1"/>
     <col min="8" max="8" width="10.6640625" customWidth="1"/>
     <col min="12" max="12" width="9.33203125" customWidth="1"/>
@@ -5900,7 +5909,7 @@
       </c>
     </row>
     <row r="20" spans="2:15" ht="15.75" customHeight="1"/>
-    <row r="23" spans="2:15">
+    <row r="23" spans="2:15" ht="13.15">
       <c r="F23" s="46" t="s">
         <v>173</v>
       </c>
@@ -5926,7 +5935,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="30" spans="2:15" ht="14.4">
+    <row r="30" spans="2:15" ht="14.25">
       <c r="F30" s="45" t="s">
         <v>38</v>
       </c>
@@ -5958,7 +5967,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="31" spans="2:15" ht="14.4">
+    <row r="31" spans="2:15" ht="14.25">
       <c r="F31" s="48" t="s">
         <v>159</v>
       </c>
@@ -5978,7 +5987,7 @@
       <c r="N31" s="49"/>
       <c r="O31" s="49"/>
     </row>
-    <row r="32" spans="2:15" ht="14.4">
+    <row r="32" spans="2:15" ht="14.25">
       <c r="F32" s="48" t="s">
         <v>161</v>
       </c>
@@ -5998,7 +6007,7 @@
       <c r="N32" s="49"/>
       <c r="O32" s="49"/>
     </row>
-    <row r="33" spans="6:15" ht="14.4">
+    <row r="33" spans="6:15" ht="14.25">
       <c r="F33" s="48" t="s">
         <v>163</v>
       </c>
@@ -6020,7 +6029,7 @@
       <c r="N33" s="49"/>
       <c r="O33" s="49"/>
     </row>
-    <row r="34" spans="6:15" ht="14.4">
+    <row r="34" spans="6:15" ht="14.25">
       <c r="F34" s="48" t="s">
         <v>165</v>
       </c>
@@ -6052,7 +6061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="6:15" ht="14.4">
+    <row r="35" spans="6:15" ht="14.25">
       <c r="F35" s="48" t="s">
         <v>167</v>
       </c>
@@ -6084,7 +6093,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="6:15" ht="14.4">
+    <row r="36" spans="6:15" ht="14.25">
       <c r="F36" s="48" t="s">
         <v>169</v>
       </c>
@@ -6108,7 +6117,7 @@
       <c r="N36" s="49"/>
       <c r="O36" s="49"/>
     </row>
-    <row r="37" spans="6:15" ht="14.4">
+    <row r="37" spans="6:15" ht="14.25">
       <c r="F37" s="48" t="s">
         <v>171</v>
       </c>
@@ -6149,20 +6158,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:J233"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" style="7" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="7" customWidth="1"/>
+    <col min="1" max="1" width="2.86328125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="12.86328125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="8.86328125" style="7" customWidth="1"/>
     <col min="4" max="4" width="14" style="7" customWidth="1"/>
-    <col min="5" max="5" width="5.44140625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="5.46484375" style="7" customWidth="1"/>
     <col min="6" max="6" width="13.6640625" style="7" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.88671875" style="7" customWidth="1"/>
-    <col min="9" max="16384" width="9.109375" style="7"/>
+    <col min="7" max="7" width="10.46484375" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.86328125" style="7" customWidth="1"/>
+    <col min="9" max="16384" width="9.1328125" style="7"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="17.399999999999999">
+    <row r="3" spans="2:10" ht="17.25">
       <c r="B3" s="5" t="s">
         <v>26</v>
       </c>
@@ -10282,24 +10291,24 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42C8BD73-0DF8-4F72-B0F0-D4FB13B1EA60}">
-  <dimension ref="B2:D4"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <dimension ref="B2:D7"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="38"/>
-    <col min="2" max="2" width="10.109375" style="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" style="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" style="38" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.109375" style="38"/>
+    <col min="1" max="1" width="9.1328125" style="38"/>
+    <col min="2" max="2" width="10.1328125" style="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1328125" style="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.46484375" style="38" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.1328125" style="38"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4">
+    <row r="2" spans="2:4" ht="13.15">
       <c r="B2" s="36" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
     </row>
-    <row r="3" spans="2:4">
+    <row r="3" spans="2:4" ht="13.15">
       <c r="B3" s="39" t="s">
         <v>12</v>
       </c>
@@ -10310,14 +10319,47 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.8" thickBot="1">
-      <c r="B4" s="40" t="s">
+    <row r="4" spans="2:4">
+      <c r="B4" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="38" t="s">
+        <v>400</v>
+      </c>
+      <c r="D4" s="38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>402</v>
+      </c>
+      <c r="D5" s="38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>401</v>
+      </c>
+      <c r="D6" s="38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="13.15" thickBot="1">
+      <c r="B7" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="D4" s="40">
+      <c r="D7" s="40">
         <v>1</v>
       </c>
     </row>
@@ -10333,15 +10375,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E800C01780957C4993EAD0B0EDC5E8FF" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1ada55d1baadc38a59b37f146ad1da21">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="95645557-b925-4e14-b9c3-bb0dccab904e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a6148ddbe210b331c9edc42bf7e0f90a" ns2:_="">
     <xsd:import namespace="95645557-b925-4e14-b9c3-bb0dccab904e"/>
@@ -10485,6 +10518,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{641C9249-69FC-4D80-A8BF-F45CF9C8F019}">
   <ds:schemaRefs>
@@ -10502,14 +10544,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF4A66DF-54A6-4E03-963C-8A735A5B845A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38EE394D-E8DA-413E-B5EF-6DF7212C84CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10525,4 +10559,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF4A66DF-54A6-4E03-963C-8A735A5B845A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>